--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/maule.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M566"/>
+  <dimension ref="A1:M571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2229.27</v>
+        <v>2210.39</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>7431.92</v>
+        <v>7393.73</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1404.28</v>
+        <v>1389.57</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>23353.14</v>
+        <v>23108.58</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>10717.74</v>
+        <v>10605.5</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3423.63</v>
+        <v>3404.91</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>768.8099999999999</v>
+        <v>764.61</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3303.38</v>
+        <v>3285.33</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>10658.18</v>
+        <v>10599.81</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>14066.66</v>
+        <v>13989.62</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3032.85</v>
+        <v>3016.24</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4931.64</v>
+        <v>4925.36</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3126.56</v>
+        <v>3122.58</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2547.16</v>
+        <v>2543.92</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>6394.9</v>
+        <v>6386.76</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1414.73</v>
+        <v>1412.93</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2131.45</v>
+        <v>2128.74</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>9339.940000000001</v>
+        <v>9328.049999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>749.9400000000001</v>
+        <v>748.99</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>6147.36</v>
+        <v>6169.3</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1212.26</v>
+        <v>1216.59</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2515.96</v>
+        <v>2524.94</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>826.0599999999999</v>
+        <v>829.01</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>20807.1</v>
+        <v>20881.35</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1864.68</v>
+        <v>1871.34</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>7313.33</v>
+        <v>7339.43</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1018.31</v>
+        <v>1029.39</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2400.13</v>
+        <v>2426.23</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2538.47</v>
+        <v>2546.82</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>6409.76</v>
+        <v>6430.85</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2671.53</v>
+        <v>2680.31</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>8909.33</v>
+        <v>9063.120000000001</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>969.53</v>
+        <v>986.26</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>977.73</v>
+        <v>994.61</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2752.44</v>
+        <v>2799.95</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1177.98</v>
+        <v>1186.15</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2567.01</v>
+        <v>2578.96</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2632.71</v>
+        <v>2644.97</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>4845.82</v>
+        <v>4868.39</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1490.27</v>
+        <v>1497.21</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2231.97</v>
+        <v>2242.36</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>7891.09</v>
+        <v>7947.98</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>5163.52</v>
+        <v>5200.75</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2423.78</v>
+        <v>2441.25</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1231.61</v>
+        <v>1240.49</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2920.96</v>
+        <v>2915.78</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>751.75</v>
+        <v>750.41</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2243.96</v>
+        <v>2239.98</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>749.4</v>
+        <v>748.0700000000001</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1598.88</v>
+        <v>1592.29</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>8046.78</v>
+        <v>8013.62</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2566.54</v>
+        <v>2555.96</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1781.06</v>
+        <v>1773.72</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>22665.27</v>
+        <v>22782.32</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2285.09</v>
+        <v>2296.89</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>764.04</v>
+        <v>769.4299999999999</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2446.6</v>
+        <v>2414.98</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>12718.75</v>
+        <v>12557.19</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>2470.22</v>
+        <v>2438.84</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>12622.15</v>
+        <v>12461.82</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>876.7</v>
+        <v>867.97</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>836.64</v>
+        <v>833.64</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>962.5599999999999</v>
+        <v>959.11</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4349.66</v>
+        <v>4334.07</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>4534.05</v>
+        <v>4517.8</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1584.06</v>
+        <v>1578.38</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3873.11</v>
+        <v>3864.73</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2602.71</v>
+        <v>2591.8</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>4768.25</v>
+        <v>4748.26</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>7889.65</v>
+        <v>7856.57</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>9358.15</v>
+        <v>9249.84</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1089.92</v>
+        <v>1077.31</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>843.63</v>
+        <v>833.87</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2369.19</v>
+        <v>2341.77</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>7177.44</v>
+        <v>7094.37</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>4588.74</v>
+        <v>4535.63</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>35459.85</v>
+        <v>35159.47</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>5303.6</v>
+        <v>5299.34</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>3468.7</v>
+        <v>3465.91</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2049.95</v>
+        <v>2048.3</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>4230.34</v>
+        <v>4226.94</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>5681.59</v>
+        <v>5677.02</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>4984.72</v>
+        <v>4980.71</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>6612.51</v>
+        <v>6637.89</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1689.93</v>
+        <v>1696.42</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>764.92</v>
+        <v>768.39</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>4471.21</v>
+        <v>4491.48</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2788.16</v>
+        <v>2784.25</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2114.6</v>
+        <v>2111.64</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1302.3</v>
+        <v>1303.97</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1237.07</v>
+        <v>1247.64</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>3170.73</v>
+        <v>3197.82</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>3793</v>
+        <v>3833.69</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>9313.08</v>
+        <v>9427.540000000001</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1600.37</v>
+        <v>1620.04</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>14563.54</v>
+        <v>14750.68</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1693.03</v>
+        <v>1714.78</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>5419.05</v>
+        <v>5448.69</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>6329.78</v>
+        <v>6364.39</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>3845.72</v>
+        <v>3866.75</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>9182.42</v>
+        <v>9232.639999999999</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>860.39</v>
+        <v>865.09</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>13527.54</v>
+        <v>13211.09</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>3264.47</v>
+        <v>3217.68</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>4714.42</v>
+        <v>4646.85</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>3295.95</v>
+        <v>3254.11</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1985.65</v>
+        <v>1960.45</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>4347.22</v>
+        <v>4284.57</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>6261.47</v>
+        <v>6171.24</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>5144.91</v>
+        <v>5070.78</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>3039.73</v>
+        <v>2995.93</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2551.6</v>
+        <v>2518.62</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>3882.46</v>
+        <v>3832.28</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>24373.65</v>
+        <v>24058.64</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>3677.16</v>
+        <v>3629.64</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2713.39</v>
+        <v>2678.33</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>12509.94</v>
+        <v>12485.31</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>795.37</v>
+        <v>793.8099999999999</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1542.51</v>
+        <v>1539.47</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>6580.91</v>
+        <v>6567.95</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>5859.75</v>
+        <v>5859.78</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>6263.95</v>
+        <v>6263.99</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2685.68</v>
+        <v>2685.7</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>10928.7</v>
+        <v>10921.24</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>8938.809999999999</v>
+        <v>8932.700000000001</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>5615.18</v>
+        <v>5611.34</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1722.47</v>
+        <v>1716.56</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>1439.46</v>
+        <v>1431.85</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2563.83</v>
+        <v>2550.28</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>2376.13</v>
+        <v>2363.58</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>6038.24</v>
+        <v>6006.34</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>4761.72</v>
+        <v>4736.57</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1762.39</v>
+        <v>1753.08</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>35200.62</v>
+        <v>35014.67</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1668.04</v>
+        <v>1659.23</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>799.16</v>
+        <v>794.9400000000001</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>3157.45</v>
+        <v>3140.77</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1906.77</v>
+        <v>1894.82</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1147.51</v>
+        <v>1140.32</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>6633.56</v>
+        <v>6591.99</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2140.47</v>
+        <v>2154.5</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>39427.82</v>
+        <v>39686.22</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>6269.28</v>
+        <v>6310.37</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>8001.28</v>
+        <v>8109.02</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>65238.91</v>
+        <v>66117.44</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>29879.92</v>
+        <v>30282.3</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>18119.93</v>
+        <v>18363.94</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>12645.06</v>
+        <v>12815.35</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>832.14</v>
+        <v>844.8099999999999</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1063</v>
+        <v>1088.85</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>800.7</v>
+        <v>820.17</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2023.64</v>
+        <v>2072.85</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>2373.36</v>
+        <v>2431.08</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>12894.97</v>
+        <v>13208.55</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>2480.57</v>
+        <v>2540.89</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>4012.77</v>
+        <v>4114.21</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>6804.87</v>
+        <v>6976.9</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2010.59</v>
+        <v>2061.41</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>913.95</v>
+        <v>937.05</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>4014.39</v>
+        <v>4136.12</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>7914.18</v>
+        <v>8154.17</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>6667.09</v>
+        <v>6865.25</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>38152.02</v>
+        <v>39286.01</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>3054.32</v>
+        <v>3145.1</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>8496.27</v>
+        <v>8748.799999999999</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>14397.54</v>
+        <v>14825.48</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>2889.53</v>
+        <v>2975.41</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>6309.94</v>
+        <v>6497.49</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>922.04</v>
+        <v>949.45</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>1792.55</v>
+        <v>1786.17</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>6164.94</v>
+        <v>6142.99</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>11699.83</v>
+        <v>11612.27</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>3373.56</v>
+        <v>3383.33</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>3480.19</v>
+        <v>3490.28</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>4472.43</v>
+        <v>4485.38</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>4279.48</v>
+        <v>4291.88</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1427.47</v>
+        <v>1434.84</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>2579.7</v>
+        <v>2593.03</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>1019.36</v>
+        <v>1024.62</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>2755.06</v>
+        <v>2743.45</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>1159.78</v>
+        <v>1154.89</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>3627.65</v>
+        <v>3612.35</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>4667.26</v>
+        <v>4709.71</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>5500.42</v>
+        <v>5538.71</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>3224.42</v>
+        <v>3246.87</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>1216.99</v>
+        <v>1225.46</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>3097.53</v>
+        <v>3119.1</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>8691.889999999999</v>
+        <v>8752.4</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1077.63</v>
+        <v>1084.72</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1702.13</v>
+        <v>1713.34</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1739.63</v>
+        <v>1751.09</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>10313.28</v>
+        <v>10381.2</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>4492.97</v>
+        <v>4532.99</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>6421.16</v>
+        <v>6478.36</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>14405.29</v>
+        <v>14380.6</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>16658.51</v>
+        <v>16641.33</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>10265.24</v>
+        <v>10254.65</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>2475.58</v>
+        <v>2473.03</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>1160.01</v>
+        <v>1158.82</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>8226.790000000001</v>
+        <v>8218.309999999999</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>4672.2</v>
+        <v>4667.38</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>11482.54</v>
+        <v>11470.7</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>32538.26</v>
+        <v>32305.16</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>9126.67</v>
+        <v>9113.25</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>25135.75</v>
+        <v>25098.77</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1839.91</v>
+        <v>1829.89</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>2733.35</v>
+        <v>2717.24</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>818.4299999999999</v>
+        <v>813.61</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>1335.76</v>
+        <v>1327.89</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>885.27</v>
+        <v>879.89</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>4774.8</v>
+        <v>4756.37</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>1875.86</v>
+        <v>1868.62</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>11388.95</v>
+        <v>11344.99</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>5294.62</v>
+        <v>5274.18</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>28187.41</v>
+        <v>28333.35</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>3441.83</v>
+        <v>3459.65</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>912.66</v>
+        <v>917.39</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>22768.84</v>
+        <v>22886.72</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>65758.33</v>
+        <v>65821.71000000001</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>18869.7</v>
+        <v>18887.89</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>7663.61</v>
+        <v>8002.05</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>7424.38</v>
+        <v>7752.25</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>2429.66</v>
+        <v>2536.96</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>6033.11</v>
+        <v>6299.54</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>2246.15</v>
+        <v>2311.39</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>4656.91</v>
+        <v>4733.66</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>2398.69</v>
+        <v>2438.22</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>771.63</v>
+        <v>784.35</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>1037.92</v>
+        <v>1055.03</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>3207.22</v>
+        <v>3260.08</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>12894.05</v>
+        <v>12728.05</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>6473.84</v>
+        <v>6428.15</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>6947.75</v>
+        <v>6898.72</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>4114.56</v>
+        <v>4085.52</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>9046.76</v>
+        <v>9210.790000000001</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>1463.01</v>
+        <v>1489.53</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>5777</v>
+        <v>5881.74</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>1252.1</v>
+        <v>1274.8</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>2477.99</v>
+        <v>2522.92</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>2071.95</v>
+        <v>2104.4</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>5871.35</v>
+        <v>5963.32</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>2328.7</v>
+        <v>2365.18</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>3796.84</v>
+        <v>3796.64</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>2205.55</v>
+        <v>2205.44</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>1591.9</v>
+        <v>1591.81</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>20631.5</v>
+        <v>20630.44</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>6777.91</v>
+        <v>6777.56</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>32951.44</v>
+        <v>32949.74</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>8814.02</v>
+        <v>8821.620000000001</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>6554.14</v>
+        <v>6559.78</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>2092.55</v>
+        <v>2101.2</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>3070.45</v>
+        <v>3083.14</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>16482.24</v>
+        <v>16550.33</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>2504.6</v>
+        <v>2497.69</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>4804.29</v>
+        <v>4748.82</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>1542.58</v>
+        <v>1524.77</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>16220.05</v>
+        <v>16032.8</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>6404.84</v>
+        <v>6309.31</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>2532.05</v>
+        <v>2494.28</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>3041.55</v>
+        <v>3024.08</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>786.05</v>
+        <v>781.54</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>3431.53</v>
+        <v>3409.55</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>792.23</v>
+        <v>787.15</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>4475.71</v>
+        <v>4456.43</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>1916.26</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>780.96</v>
+        <v>777.59</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>1231.4</v>
+        <v>1226.1</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>3953.45</v>
+        <v>3936.42</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>1711.72</v>
+        <v>1704.35</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>768.72</v>
+        <v>765.4</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>3229.09</v>
+        <v>3182.37</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>1426.01</v>
+        <v>1395.33</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>3467.94</v>
+        <v>3393.32</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>18080.71</v>
+        <v>17659.98</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>809.9400000000001</v>
+        <v>791.09</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>3250</v>
+        <v>3174.37</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>4763.17</v>
+        <v>4652.34</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>7638.68</v>
+        <v>7395.11</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>1025.01</v>
+        <v>992.33</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>2512.21</v>
+        <v>2432.11</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>7082.31</v>
+        <v>6856.48</v>
       </c>
     </row>
     <row r="283">
@@ -17710,13 +17710,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>1107.34</v>
+        <v>1072.03</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1738-129-CM26</t>
+          <t>2045-112-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -17736,17 +17736,17 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>69.130.200-8</t>
+          <t>61.606.910-1</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEGRE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -17756,12 +17756,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>RUSTIC PINK SPA</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.649.678-2</t>
         </is>
       </c>
       <c r="K284" t="inlineStr"/>
@@ -17771,13 +17771,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>2744.08</v>
+        <v>837.33</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1511-368-CM26</t>
+          <t>1738-129-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -17797,17 +17797,17 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>61.606.911-k</t>
+          <t>69.130.200-8</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEGRE</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -17817,12 +17817,12 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>78.906.980-8</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K285" t="inlineStr"/>
@@ -17832,13 +17832,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>5150.79</v>
+        <v>2689.97</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2045-112-CM26</t>
+          <t>1511-368-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -17863,12 +17863,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>61.606.910-1</t>
+          <t>61.606.911-k</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -17878,12 +17878,12 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>RUSTIC PINK SPA</t>
+          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>77.649.678-2</t>
+          <t>78.906.980-8</t>
         </is>
       </c>
       <c r="K286" t="inlineStr"/>
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>854.1799999999999</v>
+        <v>5049.21</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>1740.5</v>
+        <v>1694.67</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>1768.1</v>
+        <v>1736.03</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>2458.55</v>
+        <v>2413.97</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>2672.1</v>
+        <v>2623.64</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>3751.32</v>
+        <v>3683.29</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>3831.19</v>
+        <v>3728.6</v>
       </c>
     </row>
     <row r="293">
@@ -18320,13 +18320,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>2004.61</v>
+        <v>1950.93</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>4401-260-CM26</t>
+          <t>4716-2-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18346,17 +18346,17 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -18366,12 +18366,12 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
+          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>78.906.980-8</t>
+          <t>89.842.300-k</t>
         </is>
       </c>
       <c r="K294" t="inlineStr"/>
@@ -18381,13 +18381,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>5568.17</v>
+        <v>1119.91</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>4716-2-CM26</t>
+          <t>4452-268-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -18407,17 +18407,17 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18442,13 +18442,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>1116.65</v>
+        <v>8423.639999999999</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>4452-268-CM26</t>
+          <t>4452-269-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -18468,7 +18468,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -18488,12 +18488,12 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>89.842.300-k</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K296" t="inlineStr"/>
@@ -18503,13 +18503,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>8399.190000000001</v>
+        <v>8586.59</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>4452-269-CM26</t>
+          <t>2436-403-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -18529,17 +18529,17 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -18549,12 +18549,12 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>78.906.980-8</t>
         </is>
       </c>
       <c r="K297" t="inlineStr"/>
@@ -18564,13 +18564,13 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>8561.66</v>
+        <v>13588.01</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2436-403-CM26</t>
+          <t>4401-260-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -18595,12 +18595,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>13548.57</v>
+        <v>5584.38</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>13162.68</v>
+        <v>13217.38</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>3617.54</v>
+        <v>3632.57</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>5419.44</v>
+        <v>5441.97</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>2768.13</v>
+        <v>2779.63</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>2590.09</v>
+        <v>2612.07</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>1090.83</v>
+        <v>1100.08</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>3360.04</v>
+        <v>3388.56</v>
       </c>
     </row>
     <row r="306">
@@ -19113,13 +19113,13 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>824.67</v>
+        <v>831.66</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1209004-75-CM26</t>
+          <t>2292-6345-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -19139,17 +19139,17 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -19159,12 +19159,12 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>JIREH SOLUTION SPA</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>78.061.716-0</t>
         </is>
       </c>
       <c r="K307" t="inlineStr"/>
@@ -19174,13 +19174,13 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>3358.19</v>
+        <v>1006.2</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2292-6345-CM26</t>
+          <t>1209004-73-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19200,17 +19200,17 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -19220,12 +19220,12 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>JIREH SOLUTION SPA</t>
+          <t>EQUILIBRIUM SPA</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>78.061.716-0</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K308" t="inlineStr"/>
@@ -19235,13 +19235,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>1007.88</v>
+        <v>3352.57</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1209004-73-CM26</t>
+          <t>1209004-74-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -19296,13 +19296,13 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>3358.19</v>
+        <v>3352.57</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>1209004-74-CM26</t>
+          <t>1209004-75-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>3358.19</v>
+        <v>3352.57</v>
       </c>
     </row>
     <row r="311">
@@ -19418,13 +19418,13 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>12037.75</v>
+        <v>12017.63</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2827-296-CM26</t>
+          <t>2445-1882-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -19444,17 +19444,17 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -19464,12 +19464,12 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>77.189.387-2</t>
+          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>77.189.387-2</t>
+          <t>78.906.980-8</t>
         </is>
       </c>
       <c r="K312" t="inlineStr"/>
@@ -19479,13 +19479,13 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>1756.86</v>
+        <v>27429.96</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2445-1880-CM26</t>
+          <t>2445-1881-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -19505,7 +19505,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -19525,12 +19525,12 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.205.722-9</t>
         </is>
       </c>
       <c r="K313" t="inlineStr"/>
@@ -19540,13 +19540,13 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>3126.07</v>
+        <v>2959.74</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2445-1882-CM26</t>
+          <t>2445-1880-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -19586,12 +19586,12 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>78.906.980-8</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K314" t="inlineStr"/>
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>27096.47</v>
+        <v>3164.54</v>
       </c>
     </row>
     <row r="315">
@@ -19662,13 +19662,13 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>2090.85</v>
+        <v>2116.58</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2445-1881-CM26</t>
+          <t>2827-296-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -19693,12 +19693,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -19708,12 +19708,12 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>77.189.387-2</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
+          <t>77.189.387-2</t>
         </is>
       </c>
       <c r="K316" t="inlineStr"/>
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>2923.76</v>
+        <v>1778.49</v>
       </c>
     </row>
     <row r="317">
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>14109.77</v>
+        <v>14283.42</v>
       </c>
     </row>
     <row r="318">
@@ -19845,13 +19845,13 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>860.02</v>
+        <v>870.6</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>902-98-CM26</t>
+          <t>2436-418-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -19876,12 +19876,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -19891,12 +19891,12 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K319" t="inlineStr"/>
@@ -19906,13 +19906,13 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>2652.27</v>
+        <v>2657.8</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2436-418-CM26</t>
+          <t>4085-228-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -19932,17 +19932,17 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.130.600-3</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -19952,12 +19952,12 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K320" t="inlineStr"/>
@@ -19967,13 +19967,13 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>2625.49</v>
+        <v>2638.9</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>4085-228-CM26</t>
+          <t>902-98-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -19993,17 +19993,17 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>69.130.600-3</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONGAVI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>2606.81</v>
+        <v>2684.91</v>
       </c>
     </row>
     <row r="322">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>2025.77</v>
+        <v>2052.74</v>
       </c>
     </row>
     <row r="323">
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>2745.52</v>
+        <v>2782.07</v>
       </c>
     </row>
     <row r="324">
@@ -20211,13 +20211,13 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>1656.97</v>
+        <v>1679.03</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>712830-44-CM26</t>
+          <t>2292-6379-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -20242,12 +20242,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -20257,12 +20257,12 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K325" t="inlineStr"/>
@@ -20272,13 +20272,13 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>954.24</v>
+        <v>4780.28</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2292-6379-CM26</t>
+          <t>712830-44-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -20303,12 +20303,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -20318,12 +20318,12 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K326" t="inlineStr"/>
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>4717.48</v>
+        <v>966.9400000000001</v>
       </c>
     </row>
     <row r="327">
@@ -20394,7 +20394,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>3120.43</v>
+        <v>3161.15</v>
       </c>
     </row>
     <row r="328">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>1823.1</v>
+        <v>1846.89</v>
       </c>
     </row>
     <row r="329">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>2534.83</v>
+        <v>2567.91</v>
       </c>
     </row>
     <row r="330">
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>13601.52</v>
+        <v>13779.02</v>
       </c>
     </row>
     <row r="331">
@@ -20638,7 +20638,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>10032.15</v>
+        <v>10163.07</v>
       </c>
     </row>
     <row r="332">
@@ -20699,13 +20699,13 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>1102.99</v>
+        <v>1117.38</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2825-130-CM26</t>
+          <t>902-117-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -20730,12 +20730,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -20745,12 +20745,12 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K333" t="inlineStr"/>
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>782.27</v>
+        <v>1255.65</v>
       </c>
     </row>
     <row r="334">
@@ -20821,13 +20821,13 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>2905.37</v>
+        <v>2976.87</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>902-117-CM26</t>
+          <t>2825-130-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -20852,12 +20852,12 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -20867,12 +20867,12 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K335" t="inlineStr"/>
@@ -20882,13 +20882,13 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>1225.49</v>
+        <v>801.52</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>1087105-11-CM26</t>
+          <t>4172-139-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -20913,12 +20913,12 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>69.130.500-7</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -20928,12 +20928,12 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K336" t="inlineStr"/>
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>787.48</v>
+        <v>3787.15</v>
       </c>
     </row>
     <row r="337">
@@ -21004,13 +21004,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>5885.37</v>
+        <v>6030.21</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>4172-139-CM26</t>
+          <t>1087105-11-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -21035,12 +21035,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>69.130.500-7</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -21050,12 +21050,12 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K338" t="inlineStr"/>
@@ -21065,7 +21065,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>3696.19</v>
+        <v>806.86</v>
       </c>
     </row>
     <row r="339">
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>5245.34</v>
+        <v>5344.55</v>
       </c>
     </row>
     <row r="340">
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>1149.43</v>
+        <v>1171.17</v>
       </c>
     </row>
     <row r="341">
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>2955.5</v>
+        <v>3011.39</v>
       </c>
     </row>
     <row r="342">
@@ -21309,7 +21309,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>841.02</v>
+        <v>850.58</v>
       </c>
     </row>
     <row r="343">
@@ -21370,7 +21370,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>2908.78</v>
+        <v>2941.86</v>
       </c>
     </row>
     <row r="344">
@@ -21431,7 +21431,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>3160.95</v>
+        <v>3196.89</v>
       </c>
     </row>
     <row r="345">
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>1655.21</v>
+        <v>1674.03</v>
       </c>
     </row>
     <row r="346">
@@ -21553,7 +21553,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>2834.82</v>
+        <v>2867.06</v>
       </c>
     </row>
     <row r="347">
@@ -21614,13 +21614,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>1582.57</v>
+        <v>1600.57</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>4404-67-CM26</t>
+          <t>2436-450-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -21640,17 +21640,17 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -21660,12 +21660,12 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
+          <t>PROVEEDORA KENUA SPA</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>89.842.300-k</t>
+          <t>78.212.867-1</t>
         </is>
       </c>
       <c r="K348" t="inlineStr"/>
@@ -21675,13 +21675,13 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>10485.83</v>
+        <v>9392.5</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2436-450-CM26</t>
+          <t>2595-161-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -21701,17 +21701,17 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -21721,12 +21721,12 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>PROVEEDORA KENUA SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>78.212.867-1</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K349" t="inlineStr"/>
@@ -21736,13 +21736,13 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>9308.65</v>
+        <v>2222.94</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2595-161-CM26</t>
+          <t>4404-65-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -21767,12 +21767,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -21782,12 +21782,12 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>78.906.980-8</t>
         </is>
       </c>
       <c r="K350" t="inlineStr"/>
@@ -21797,13 +21797,13 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>2203.09</v>
+        <v>10058.29</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>4404-65-CM26</t>
+          <t>3251-136-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -21828,12 +21828,12 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.252.700-3</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE PELLUHUE</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -21843,12 +21843,12 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
+          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>78.906.980-8</t>
+          <t>89.842.300-k</t>
         </is>
       </c>
       <c r="K351" t="inlineStr"/>
@@ -21858,13 +21858,13 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>9968.49</v>
+        <v>2576.93</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>3251-136-CM26</t>
+          <t>4404-67-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -21889,12 +21889,12 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>69.252.700-3</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELLUHUE</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>2553.92</v>
+        <v>10580.28</v>
       </c>
     </row>
     <row r="353">
@@ -21980,7 +21980,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>10395.32</v>
+        <v>10488.97</v>
       </c>
     </row>
     <row r="354">
@@ -22041,7 +22041,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>886.0599999999999</v>
+        <v>891.72</v>
       </c>
     </row>
     <row r="355">
@@ -22102,7 +22102,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>5927.36</v>
+        <v>5965.27</v>
       </c>
     </row>
     <row r="356">
@@ -22163,7 +22163,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>825.26</v>
+        <v>827.86</v>
       </c>
     </row>
     <row r="357">
@@ -22224,7 +22224,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>788.49</v>
+        <v>790.98</v>
       </c>
     </row>
     <row r="358">
@@ -22285,7 +22285,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>1028.52</v>
+        <v>1032.78</v>
       </c>
     </row>
     <row r="359">
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>2802.55</v>
+        <v>2814.17</v>
       </c>
     </row>
     <row r="360">
@@ -22407,7 +22407,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>1197.19</v>
+        <v>1202.15</v>
       </c>
     </row>
     <row r="361">
@@ -22468,13 +22468,13 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>7237.14</v>
+        <v>7267.13</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>1272260-11-CM26</t>
+          <t>2291-712-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -22499,12 +22499,12 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>73.464.000-k</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Economato Centro Cumplimiento Penitenciario Talca</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -22514,12 +22514,12 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SURTI VENTAS S.A.</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.462.500-5</t>
         </is>
       </c>
       <c r="K362" t="inlineStr"/>
@@ -22529,13 +22529,13 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>862.79</v>
+        <v>3156.09</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>1075337-7849-CM26</t>
+          <t>1421-160-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -22560,12 +22560,12 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -22575,12 +22575,12 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>89.842.300-k</t>
         </is>
       </c>
       <c r="K363" t="inlineStr"/>
@@ -22590,13 +22590,13 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>786.52</v>
+        <v>3038.58</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>1421-160-CM26</t>
+          <t>2311-124-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -22621,12 +22621,12 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.110.100-2</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>IMunicipalidad de Molina</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -22636,12 +22636,12 @@
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>89.842.300-k</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K364" t="inlineStr"/>
@@ -22651,13 +22651,13 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>3032.3</v>
+        <v>3144.76</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2311-124-CM26</t>
+          <t>1272260-11-CM26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -22682,12 +22682,12 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>69.110.100-2</t>
+          <t>73.464.000-k</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t>Economato Centro Cumplimiento Penitenciario Talca</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -22697,12 +22697,12 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K365" t="inlineStr"/>
@@ -22712,13 +22712,13 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>3138.26</v>
+        <v>864.58</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2291-712-CM26</t>
+          <t>1075337-7849-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -22743,12 +22743,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -22758,12 +22758,12 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>SURTI VENTAS S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>76.462.500-5</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K366" t="inlineStr"/>
@@ -22773,7 +22773,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>3149.56</v>
+        <v>788.15</v>
       </c>
     </row>
     <row r="367">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>3754.09</v>
+        <v>3737.96</v>
       </c>
     </row>
     <row r="368">
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>1754.79</v>
+        <v>1747.25</v>
       </c>
     </row>
     <row r="369">
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>4628.07</v>
+        <v>4608.19</v>
       </c>
     </row>
     <row r="370">
@@ -23017,7 +23017,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>28683.5</v>
+        <v>28511.6</v>
       </c>
     </row>
     <row r="371">
@@ -23078,13 +23078,13 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>37036.26</v>
+        <v>36532.73</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>902-132-CM26</t>
+          <t>3385-99-CM26</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -23104,17 +23104,17 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K372" t="inlineStr"/>
@@ -23139,13 +23139,13 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>3124.15</v>
+        <v>2684.13</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>3385-99-CM26</t>
+          <t>902-132-CM26</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -23165,17 +23165,17 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -23185,12 +23185,12 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K373" t="inlineStr"/>
@@ -23200,13 +23200,13 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>2707.22</v>
+        <v>3097.51</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>1506-45-CM26</t>
+          <t>1465-178-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -23226,17 +23226,17 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.606.907-1</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -23246,12 +23246,12 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>89.842.300-k</t>
         </is>
       </c>
       <c r="K374" t="inlineStr"/>
@@ -23261,13 +23261,13 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>1005.46</v>
+        <v>1524.94</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>1465-178-CM26</t>
+          <t>1506-45-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -23287,17 +23287,17 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>61.606.907-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -23307,12 +23307,12 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>89.842.300-k</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K375" t="inlineStr"/>
@@ -23322,7 +23322,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>1516.77</v>
+        <v>1010.88</v>
       </c>
     </row>
     <row r="376">
@@ -23383,7 +23383,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>2812.46</v>
+        <v>2843.92</v>
       </c>
     </row>
     <row r="377">
@@ -23444,7 +23444,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>6900.36</v>
+        <v>6977.53</v>
       </c>
     </row>
     <row r="378">
@@ -23505,7 +23505,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>1670.92</v>
+        <v>1689.61</v>
       </c>
     </row>
     <row r="379">
@@ -23566,7 +23566,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>1066.99</v>
+        <v>1078.93</v>
       </c>
     </row>
     <row r="380">
@@ -23627,7 +23627,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>6425.81</v>
+        <v>6474.48</v>
       </c>
     </row>
     <row r="381">
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>2324.26</v>
+        <v>2333.06</v>
       </c>
     </row>
     <row r="382">
@@ -23749,7 +23749,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>4895.18</v>
+        <v>4913.73</v>
       </c>
     </row>
     <row r="383">
@@ -23810,7 +23810,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>946.36</v>
+        <v>949.95</v>
       </c>
     </row>
     <row r="384">
@@ -23871,7 +23871,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>4424.61</v>
+        <v>4441.37</v>
       </c>
     </row>
     <row r="385">
@@ -23932,7 +23932,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>6885.43</v>
+        <v>6911.51</v>
       </c>
     </row>
     <row r="386">
@@ -23993,13 +23993,13 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>4496.82</v>
+        <v>4513.86</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>3806-59-CM26</t>
+          <t>3469-211-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -24019,17 +24019,17 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>69.120.200-3</t>
+          <t>69.120.300-k</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EMPEDRADO</t>
+          <t>I MUNICIPALIDAD DE CHANCO</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -24039,12 +24039,12 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>78.906.980-8</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K387" t="inlineStr"/>
@@ -24054,13 +24054,13 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>936.9400000000001</v>
+        <v>13196.04</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>3469-211-CM26</t>
+          <t>1391-848-CM26</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -24085,12 +24085,12 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>69.120.300-k</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANCO</t>
+          <t>Dirección Regional de Gendarmeria - Talca</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -24100,12 +24100,12 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K388" t="inlineStr"/>
@@ -24115,13 +24115,13 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>13229.44</v>
+        <v>833.3200000000001</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>1391-848-CM26</t>
+          <t>1426095-101-CM26</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -24141,17 +24141,17 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -24176,13 +24176,13 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>835.4299999999999</v>
+        <v>4965.42</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>1426095-101-CM26</t>
+          <t>3806-59-CM26</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -24207,12 +24207,12 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.120.200-3</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE EMPEDRADO</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -24222,12 +24222,12 @@
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>78.906.980-8</t>
         </is>
       </c>
       <c r="K390" t="inlineStr"/>
@@ -24237,13 +24237,13 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>4977.99</v>
+        <v>934.5700000000001</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>1057461-673-CM26</t>
+          <t>4089-251-CM26</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -24268,12 +24268,12 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>69.130.602-k</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -24283,12 +24283,12 @@
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>winkler limitada</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>79.722.860-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K391" t="inlineStr"/>
@@ -24298,13 +24298,13 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>792.74</v>
+        <v>2861.39</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>4089-251-CM26</t>
+          <t>1469-1243-CM26</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -24324,17 +24324,17 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>69.130.602-k</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -24344,12 +24344,12 @@
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>89.842.300-k</t>
         </is>
       </c>
       <c r="K392" t="inlineStr"/>
@@ -24359,13 +24359,13 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>2834.46</v>
+        <v>16833.7</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>4089-252-CM26</t>
+          <t>2292-6509-CM26</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -24385,17 +24385,17 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>69.130.602-k</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -24405,12 +24405,12 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K393" t="inlineStr"/>
@@ -24420,13 +24420,13 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>5882.73</v>
+        <v>3606.74</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2292-6508-CM26</t>
+          <t>1057461-673-CM26</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -24446,17 +24446,17 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -24466,12 +24466,12 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
+          <t>winkler limitada</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>89.842.300-k</t>
+          <t>79.722.860-5</t>
         </is>
       </c>
       <c r="K394" t="inlineStr"/>
@@ -24481,13 +24481,13 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>33390.02</v>
+        <v>800.27</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2292-6509-CM26</t>
+          <t>4089-252-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -24507,17 +24507,17 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.130.602-k</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -24527,12 +24527,12 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K395" t="inlineStr"/>
@@ -24542,13 +24542,13 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>3572.79</v>
+        <v>5938.62</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>1469-1243-CM26</t>
+          <t>2292-6508-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -24573,12 +24573,12 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -24603,7 +24603,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>16675.27</v>
+        <v>33707.25</v>
       </c>
     </row>
     <row r="397">
@@ -24664,7 +24664,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>2652.73</v>
+        <v>2672.49</v>
       </c>
     </row>
     <row r="398">
@@ -24725,7 +24725,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>2016.13</v>
+        <v>2031.15</v>
       </c>
     </row>
     <row r="399">
@@ -24786,7 +24786,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>829.8200000000001</v>
+        <v>836.01</v>
       </c>
     </row>
     <row r="400">
@@ -24847,7 +24847,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>6148.21</v>
+        <v>6194.01</v>
       </c>
     </row>
     <row r="401">
@@ -24908,7 +24908,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>1509.31</v>
+        <v>1520.56</v>
       </c>
     </row>
     <row r="402">
@@ -24969,13 +24969,13 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>800.99</v>
+        <v>793</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2335-341-CM26</t>
+          <t>4343-166-CM26</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -24995,17 +24995,17 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>69.130.301-2</t>
+          <t>61.606.912-8</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -25015,12 +25015,12 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K403" t="inlineStr"/>
@@ -25030,13 +25030,13 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>1974.77</v>
+        <v>2238.02</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>4343-166-CM26</t>
+          <t>2335-341-CM26</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -25056,17 +25056,17 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>61.606.912-8</t>
+          <t>69.130.301-2</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -25076,12 +25076,12 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K404" t="inlineStr"/>
@@ -25091,7 +25091,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>2247.88</v>
+        <v>1966.11</v>
       </c>
     </row>
     <row r="405">
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>843.15</v>
+        <v>833.97</v>
       </c>
     </row>
     <row r="406">
@@ -25213,7 +25213,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>2351.13</v>
+        <v>2325.56</v>
       </c>
     </row>
     <row r="407">
@@ -25274,7 +25274,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>1047.65</v>
+        <v>1036.25</v>
       </c>
     </row>
     <row r="408">
@@ -25335,13 +25335,13 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>11266.17</v>
+        <v>11240.6</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>4452-424-CM26</t>
+          <t>4426-11-CM26</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -25366,12 +25366,12 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>Servicio Nacional del Patrimonio Cultural</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -25381,12 +25381,12 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>89.842.300-k</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K409" t="inlineStr"/>
@@ -25396,7 +25396,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>22089.9</v>
+        <v>850.8200000000001</v>
       </c>
     </row>
     <row r="410">
@@ -25457,13 +25457,13 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>853.49</v>
+        <v>857.6799999999999</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>4426-11-CM26</t>
+          <t>4452-424-CM26</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -25488,12 +25488,12 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -25503,12 +25503,12 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>89.842.300-k</t>
         </is>
       </c>
       <c r="K411" t="inlineStr"/>
@@ -25518,7 +25518,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>846.66</v>
+        <v>22198.41</v>
       </c>
     </row>
     <row r="412">
@@ -25579,7 +25579,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>1743.89</v>
+        <v>1749.68</v>
       </c>
     </row>
     <row r="413">
@@ -25640,7 +25640,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>13333.16</v>
+        <v>13377.39</v>
       </c>
     </row>
     <row r="414">
@@ -25701,7 +25701,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>26436.61</v>
+        <v>26520.75</v>
       </c>
     </row>
     <row r="415">
@@ -25762,7 +25762,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>1228.52</v>
+        <v>1232.43</v>
       </c>
     </row>
     <row r="416">
@@ -25823,13 +25823,13 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>1180.52</v>
+        <v>1186.8</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>4401-398-CM26</t>
+          <t>4451-287-CM26</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -25849,7 +25849,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
@@ -25869,12 +25869,12 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>78.906.980-8</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K417" t="inlineStr"/>
@@ -25884,13 +25884,13 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>18902.8</v>
+        <v>1120.89</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2436-608-CM26</t>
+          <t>2440-703-CM26</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -25930,12 +25930,12 @@
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K418" t="inlineStr"/>
@@ -25945,13 +25945,13 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>2346.06</v>
+        <v>1116.67</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>1426095-117-CM26</t>
+          <t>2436-608-CM26</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -25976,12 +25976,12 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -25991,12 +25991,12 @@
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K419" t="inlineStr"/>
@@ -26006,13 +26006,13 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>869.11</v>
+        <v>2379.63</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>4451-287-CM26</t>
+          <t>4401-398-CM26</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -26032,7 +26032,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -26052,12 +26052,12 @@
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>78.906.980-8</t>
         </is>
       </c>
       <c r="K420" t="inlineStr"/>
@@ -26067,13 +26067,13 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>1105.08</v>
+        <v>19173.28</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2440-703-CM26</t>
+          <t>1426095-117-CM26</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -26098,12 +26098,12 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -26113,12 +26113,12 @@
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K421" t="inlineStr"/>
@@ -26128,13 +26128,13 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>1100.92</v>
+        <v>881.54</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>4451-303-CM26</t>
+          <t>1250343-7-CM26</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -26159,12 +26159,12 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>Dirección Regional de Gendarmeria - Talca</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -26174,12 +26174,12 @@
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>89.842.300-k</t>
         </is>
       </c>
       <c r="K422" t="inlineStr"/>
@@ -26189,13 +26189,13 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>1106.42</v>
+        <v>867.0599999999999</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>1250343-7-CM26</t>
+          <t>4168-777-CM26</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -26220,12 +26220,12 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>69.130.500-7</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -26235,12 +26235,12 @@
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
+          <t>FRANCISCO JAVIER</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>89.842.300-k</t>
+          <t>76.882.403-7</t>
         </is>
       </c>
       <c r="K423" t="inlineStr"/>
@@ -26250,13 +26250,13 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>857</v>
+        <v>4723.03</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>4168-777-CM26</t>
+          <t>1511-659-CM26</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -26281,12 +26281,12 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>69.130.500-7</t>
+          <t>61.606.911-k</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -26296,12 +26296,12 @@
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>76.882.403-7</t>
+          <t>78.906.980-8</t>
         </is>
       </c>
       <c r="K424" t="inlineStr"/>
@@ -26311,13 +26311,13 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>4668.27</v>
+        <v>3112.02</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>1511-659-CM26</t>
+          <t>4451-303-CM26</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -26342,12 +26342,12 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>61.606.911-k</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>78.906.980-8</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K425" t="inlineStr"/>
@@ -26372,13 +26372,13 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>3075.94</v>
+        <v>1119.4</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>2291-997-CM26</t>
+          <t>4134-372-CM26</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -26398,17 +26398,17 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I. Municipalidad Sagrada Familia</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -26418,12 +26418,12 @@
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA ARTÍCULOS DE ASEO, CONFITES Y LIBRERÍA PEDRO HERRERA VER</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>77.163.321-8</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K426" t="inlineStr"/>
@@ -26433,13 +26433,13 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>3840.73</v>
+        <v>3875.56</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>4134-372-CM26</t>
+          <t>2291-997-CM26</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -26459,17 +26459,17 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -26479,12 +26479,12 @@
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>DISTRIBUIDORA ARTÍCULOS DE ASEO, CONFITES Y LIBRERÍA PEDRO HERRERA VER</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>77.163.321-8</t>
         </is>
       </c>
       <c r="K427" t="inlineStr"/>
@@ -26494,13 +26494,13 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>3836.55</v>
+        <v>3879.79</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>1075337-8468-CM26</t>
+          <t>4622-16-CM26</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -26525,12 +26525,12 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -26540,12 +26540,12 @@
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K428" t="inlineStr"/>
@@ -26555,13 +26555,13 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>873.74</v>
+        <v>2119.95</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>1069417-587-CM26</t>
+          <t>1069417-596-CM26</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -26601,12 +26601,12 @@
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>77.189.387-2</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.189.387-2</t>
         </is>
       </c>
       <c r="K429" t="inlineStr"/>
@@ -26616,13 +26616,13 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>3525.67</v>
+        <v>3175.78</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>1069417-596-CM26</t>
+          <t>1075337-8468-CM26</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -26647,12 +26647,12 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>69.270.200-k</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -26662,12 +26662,12 @@
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>77.189.387-2</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>77.189.387-2</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K430" t="inlineStr"/>
@@ -26677,13 +26677,13 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>3143.81</v>
+        <v>882.63</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>4622-16-CM26</t>
+          <t>1069417-587-CM26</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -26708,12 +26708,12 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>69.270.200-k</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>Dirección  de Salud Municipal Chillán</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -26723,12 +26723,12 @@
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K431" t="inlineStr"/>
@@ -26738,7 +26738,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>2098.6</v>
+        <v>3561.52</v>
       </c>
     </row>
     <row r="432">
@@ -26799,7 +26799,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>4485.77</v>
+        <v>4527.85</v>
       </c>
     </row>
     <row r="433">
@@ -26860,7 +26860,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>1257.2</v>
+        <v>1268.99</v>
       </c>
     </row>
     <row r="434">
@@ -26921,7 +26921,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>2177.48</v>
+        <v>2160.96</v>
       </c>
     </row>
     <row r="435">
@@ -26982,7 +26982,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>11983.52</v>
+        <v>11892.61</v>
       </c>
     </row>
     <row r="436">
@@ -27043,7 +27043,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>1660.26</v>
+        <v>1647.67</v>
       </c>
     </row>
     <row r="437">
@@ -27104,13 +27104,13 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>2404.55</v>
+        <v>2386.31</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>362-327-CM26</t>
+          <t>1272257-30-CM26</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -27135,12 +27135,12 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>61.606.915-2</t>
+          <t>73.656.200-6</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Economato del C.C.P. de Curicó</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -27150,12 +27150,12 @@
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>89.842.300-k</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K438" t="inlineStr"/>
@@ -27165,13 +27165,13 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>1660.06</v>
+        <v>2392.47</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>1272257-30-CM26</t>
+          <t>362-327-CM26</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -27196,12 +27196,12 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>73.656.200-6</t>
+          <t>61.606.915-2</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>Economato del C.C.P. de Curicó</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -27211,12 +27211,12 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>89.842.300-k</t>
         </is>
       </c>
       <c r="K439" t="inlineStr"/>
@@ -27226,7 +27226,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>2433.59</v>
+        <v>1632.01</v>
       </c>
     </row>
     <row r="440">
@@ -27287,7 +27287,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>1327.59</v>
+        <v>1308.75</v>
       </c>
     </row>
     <row r="441">
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>2404.44</v>
+        <v>2370.31</v>
       </c>
     </row>
     <row r="442">
@@ -27409,7 +27409,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>2671.13</v>
+        <v>2634.42</v>
       </c>
     </row>
     <row r="443">
@@ -27470,7 +27470,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>1792.03</v>
+        <v>1767.4</v>
       </c>
     </row>
     <row r="444">
@@ -27531,7 +27531,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>1152.7</v>
+        <v>1136.86</v>
       </c>
     </row>
     <row r="445">
@@ -27592,7 +27592,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>3105.2</v>
+        <v>3062.53</v>
       </c>
     </row>
     <row r="446">
@@ -27653,7 +27653,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>1935.04</v>
+        <v>1923.04</v>
       </c>
     </row>
     <row r="447">
@@ -27714,7 +27714,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>1450.2</v>
+        <v>1441.21</v>
       </c>
     </row>
     <row r="448">
@@ -27775,7 +27775,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>1171.48</v>
+        <v>1164.21</v>
       </c>
     </row>
     <row r="449">
@@ -27836,7 +27836,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>2995.22</v>
+        <v>2976.65</v>
       </c>
     </row>
     <row r="450">
@@ -27897,7 +27897,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>918.26</v>
+        <v>922.4299999999999</v>
       </c>
     </row>
     <row r="451">
@@ -27958,7 +27958,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>1444.89</v>
+        <v>1466.4</v>
       </c>
     </row>
     <row r="452">
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>1184.7</v>
+        <v>1202.34</v>
       </c>
     </row>
     <row r="453">
@@ -28080,7 +28080,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>3565.72</v>
+        <v>3618.81</v>
       </c>
     </row>
     <row r="454">
@@ -28141,13 +28141,13 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>839.45</v>
+        <v>851.95</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>902-182-CM26</t>
+          <t>3399-110-CM26</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -28167,17 +28167,17 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.946.800-7</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -28187,12 +28187,12 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K455" t="inlineStr"/>
@@ -28202,13 +28202,13 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>854.97</v>
+        <v>1430.94</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>3399-110-CM26</t>
+          <t>902-179-CM26</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -28228,17 +28228,17 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>61.946.800-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -28248,12 +28248,12 @@
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K456" t="inlineStr"/>
@@ -28263,13 +28263,13 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>1404.24</v>
+        <v>2576.69</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>902-179-CM26</t>
+          <t>2445-2136-CM26</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -28289,17 +28289,17 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -28309,12 +28309,12 @@
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>76.029.126-9</t>
         </is>
       </c>
       <c r="K457" t="inlineStr"/>
@@ -28324,13 +28324,13 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>2528.62</v>
+        <v>4446.13</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>2445-2136-CM26</t>
+          <t>2445-2137-CM26</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -28370,12 +28370,12 @@
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K458" t="inlineStr"/>
@@ -28385,13 +28385,13 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>4363.18</v>
+        <v>5650.53</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>2445-2137-CM26</t>
+          <t>2445-2138-CM26</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -28431,12 +28431,12 @@
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K459" t="inlineStr"/>
@@ -28446,13 +28446,13 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>5545.11</v>
+        <v>5866.83</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>2445-2138-CM26</t>
+          <t>902-182-CM26</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -28472,17 +28472,17 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -28492,12 +28492,12 @@
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K460" t="inlineStr"/>
@@ -28507,7 +28507,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>5757.37</v>
+        <v>871.23</v>
       </c>
     </row>
     <row r="461">
@@ -28568,13 +28568,13 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>840.47</v>
+        <v>859.42</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>3469-264-CM26</t>
+          <t>1391-1148-CM26</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -28599,12 +28599,12 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>69.120.300-k</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANCO</t>
+          <t>Dirección Regional de Gendarmeria - Talca</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
@@ -28629,13 +28629,13 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>5722.89</v>
+        <v>1032.25</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>1391-1148-CM26</t>
+          <t>3469-264-CM26</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -28660,12 +28660,12 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>69.120.300-k</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>I MUNICIPALIDAD DE CHANCO</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
@@ -28690,7 +28690,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>1009.48</v>
+        <v>5851.95</v>
       </c>
     </row>
     <row r="464">
@@ -28751,7 +28751,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>1975.02</v>
+        <v>2019.56</v>
       </c>
     </row>
     <row r="465">
@@ -28812,7 +28812,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>2799.89</v>
+        <v>2863.04</v>
       </c>
     </row>
     <row r="466">
@@ -28873,7 +28873,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>813.98</v>
+        <v>819.6</v>
       </c>
     </row>
     <row r="467">
@@ -28934,7 +28934,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>1734.84</v>
+        <v>1746.82</v>
       </c>
     </row>
     <row r="468">
@@ -28995,7 +28995,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>13157.44</v>
+        <v>13248.28</v>
       </c>
     </row>
     <row r="469">
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>6196.79</v>
+        <v>6239.57</v>
       </c>
     </row>
     <row r="470">
@@ -29117,13 +29117,13 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>3338.82</v>
+        <v>3361.87</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>362-347-CM26</t>
+          <t>2827-456-CM26</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -29148,12 +29148,12 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>61.606.915-2</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -29178,13 +29178,13 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>1104.31</v>
+        <v>4141.08</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>2827-456-CM26</t>
+          <t>362-347-CM26</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -29209,12 +29209,12 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>61.606.915-2</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -29239,13 +29239,13 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>4128.32</v>
+        <v>1107.72</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>2595-241-CM26</t>
+          <t>1511-756-CM26</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -29270,12 +29270,12 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>61.606.911-k</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -29285,12 +29285,12 @@
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.906.980-8</t>
         </is>
       </c>
       <c r="K473" t="inlineStr"/>
@@ -29300,13 +29300,13 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>3037.62</v>
+        <v>4170.87</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>1511-756-CM26</t>
+          <t>3385-148-CM26</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -29331,12 +29331,12 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>61.606.911-k</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -29346,12 +29346,12 @@
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>78.906.980-8</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K474" t="inlineStr"/>
@@ -29361,13 +29361,13 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>4181.93</v>
+        <v>2396.73</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>3385-148-CM26</t>
+          <t>1907-38-CM26</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -29392,12 +29392,12 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>61.002.004-6</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Servicio de Registro Civil e Identificación</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -29407,12 +29407,12 @@
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K475" t="inlineStr"/>
@@ -29422,13 +29422,13 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>2403.09</v>
+        <v>8889.459999999999</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>1907-38-CM26</t>
+          <t>675-37-CM26</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -29453,12 +29453,12 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>61.002.004-6</t>
+          <t>61.402.019-9</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SEREMI Bienes Nacionales VII Región</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -29468,12 +29468,12 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>89.842.300-k</t>
         </is>
       </c>
       <c r="K476" t="inlineStr"/>
@@ -29483,13 +29483,13 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>8913.040000000001</v>
+        <v>1103.09</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>675-37-CM26</t>
+          <t>1719-53-CM26</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -29514,12 +29514,12 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>61.402.019-9</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>SEREMI Bienes Nacionales VII Región</t>
+          <t>I. Municipalidad Sagrada Familia</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -29529,12 +29529,12 @@
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>89.842.300-k</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K477" t="inlineStr"/>
@@ -29544,13 +29544,13 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>1106.01</v>
+        <v>1720.5</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>1719-53-CM26</t>
+          <t>2595-241-CM26</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -29575,12 +29575,12 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -29590,12 +29590,12 @@
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K478" t="inlineStr"/>
@@ -29605,13 +29605,13 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>1725.06</v>
+        <v>3029.59</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>2311-192-CM26</t>
+          <t>1391-1195-CM26</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -29636,12 +29636,12 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>69.110.100-2</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t>Dirección Regional de Gendarmeria - Talca</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -29651,12 +29651,12 @@
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA MALUSANT SPA</t>
+          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
         </is>
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>77.720.988-4</t>
+          <t>89.842.300-k</t>
         </is>
       </c>
       <c r="K479" t="inlineStr"/>
@@ -29666,13 +29666,13 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>7684.47</v>
+        <v>4709.18</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>4172-282-CM26</t>
+          <t>2311-192-CM26</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -29692,17 +29692,17 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>69.130.500-7</t>
+          <t>69.110.100-2</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+          <t>IMunicipalidad de Molina</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -29712,12 +29712,12 @@
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
+          <t>COMERCIALIZADORA MALUSANT SPA</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>89.842.300-k</t>
+          <t>77.720.988-4</t>
         </is>
       </c>
       <c r="K480" t="inlineStr"/>
@@ -29727,13 +29727,13 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>3051.83</v>
+        <v>7582.11</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>1391-1195-CM26</t>
+          <t>4172-282-CM26</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -29753,17 +29753,17 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>69.130.500-7</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -29788,7 +29788,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>4772.75</v>
+        <v>3011.18</v>
       </c>
     </row>
     <row r="482">
@@ -29849,7 +29849,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>6356.89</v>
+        <v>6232.47</v>
       </c>
     </row>
     <row r="483">
@@ -29910,7 +29910,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>1753.11</v>
+        <v>1718.8</v>
       </c>
     </row>
     <row r="484">
@@ -29971,7 +29971,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>16406.69</v>
+        <v>16085.55</v>
       </c>
     </row>
     <row r="485">
@@ -30032,7 +30032,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>2093.4</v>
+        <v>2052.43</v>
       </c>
     </row>
     <row r="486">
@@ -30093,13 +30093,13 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>794.47</v>
+        <v>778.92</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>4452-541-CM26</t>
+          <t>4089-365-CM26</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -30124,12 +30124,12 @@
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>69.130.602-k</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -30139,12 +30139,12 @@
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J487" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K487" t="inlineStr"/>
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>2687.23</v>
+        <v>4164.87</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>4089-364-CM26</t>
+          <t>4452-541-CM26</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -30185,12 +30185,12 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>69.130.602-k</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -30215,13 +30215,13 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>3288.17</v>
+        <v>2647.41</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>4089-365-CM26</t>
+          <t>4089-364-CM26</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -30261,12 +30261,12 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K489" t="inlineStr"/>
@@ -30276,7 +30276,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>4227.5</v>
+        <v>3239.45</v>
       </c>
     </row>
     <row r="490">
@@ -30337,7 +30337,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>988.11</v>
+        <v>973.47</v>
       </c>
     </row>
     <row r="491">
@@ -30398,7 +30398,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>2350.73</v>
+        <v>2315.91</v>
       </c>
     </row>
     <row r="492">
@@ -30459,7 +30459,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>1498.39</v>
+        <v>1476.19</v>
       </c>
     </row>
     <row r="493">
@@ -30520,7 +30520,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>4735.98</v>
+        <v>4638.64</v>
       </c>
     </row>
     <row r="494">
@@ -30581,7 +30581,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>3007.48</v>
+        <v>3036.05</v>
       </c>
     </row>
     <row r="495">
@@ -30642,7 +30642,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>813.47</v>
+        <v>821.2</v>
       </c>
     </row>
     <row r="496">
@@ -30703,7 +30703,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>778.47</v>
+        <v>781.51</v>
       </c>
     </row>
     <row r="497">
@@ -30764,13 +30764,13 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>1011.44</v>
+        <v>1015.38</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>2333-379-CM26</t>
+          <t>2310-481-CM26</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -30790,17 +30790,17 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>69.130.300-4</t>
+          <t>69.110.100-2</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LINARES</t>
+          <t>IMunicipalidad de Molina</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -30825,7 +30825,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>5351.23</v>
+        <v>1153.08</v>
       </c>
     </row>
     <row r="499">
@@ -30886,13 +30886,13 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>5547.68</v>
+        <v>5603.47</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>1469-1835-CM26</t>
+          <t>2825-293-CM26</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -30917,12 +30917,12 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
@@ -30932,12 +30932,12 @@
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>78.906.980-8</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K500" t="inlineStr"/>
@@ -30947,13 +30947,13 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>3464.43</v>
+        <v>2765.47</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>1057461-971-CM26</t>
+          <t>1272256-26-CM26</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -30978,12 +30978,12 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>65.026.068-6</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>Economato C.C.P. de Cauquenes</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
@@ -30993,12 +30993,12 @@
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>78.906.980-8</t>
         </is>
       </c>
       <c r="K501" t="inlineStr"/>
@@ -31008,13 +31008,13 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>3061.06</v>
+        <v>1423.48</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>1057461-972-CM26</t>
+          <t>1075337-8840-CM26</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -31039,12 +31039,12 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -31054,12 +31054,12 @@
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.906.980-8</t>
         </is>
       </c>
       <c r="K502" t="inlineStr"/>
@@ -31069,13 +31069,13 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>2220.99</v>
+        <v>9744.42</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>1057461-973-CM26</t>
+          <t>2333-379-CM26</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -31100,12 +31100,12 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>69.130.300-4</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
@@ -31115,12 +31115,12 @@
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>winkler limitada</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>79.722.860-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K503" t="inlineStr"/>
@@ -31130,13 +31130,13 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>841.92</v>
+        <v>5405.05</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>1075337-8840-CM26</t>
+          <t>1057461-972-CM26</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -31161,12 +31161,12 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
@@ -31176,12 +31176,12 @@
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>78.906.980-8</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K504" t="inlineStr"/>
@@ -31191,13 +31191,13 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>9647.389999999999</v>
+        <v>2243.33</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>2825-293-CM26</t>
+          <t>1057461-971-CM26</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -31217,17 +31217,17 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -31237,12 +31237,12 @@
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K505" t="inlineStr"/>
@@ -31252,13 +31252,13 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>2737.93</v>
+        <v>3091.84</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>2310-481-CM26</t>
+          <t>1469-1835-CM26</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -31283,12 +31283,12 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>69.110.100-2</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>78.906.980-8</t>
         </is>
       </c>
       <c r="K506" t="inlineStr"/>
@@ -31313,13 +31313,13 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>1141.6</v>
+        <v>3499.27</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>1272256-26-CM26</t>
+          <t>1057461-973-CM26</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -31344,12 +31344,12 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>65.026.068-6</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>Economato C.C.P. de Cauquenes</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
@@ -31359,12 +31359,12 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
+          <t>winkler limitada</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>78.906.980-8</t>
+          <t>79.722.860-5</t>
         </is>
       </c>
       <c r="K507" t="inlineStr"/>
@@ -31374,7 +31374,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>1409.31</v>
+        <v>850.39</v>
       </c>
     </row>
     <row r="508">
@@ -31435,7 +31435,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>4916.66</v>
+        <v>4965.89</v>
       </c>
     </row>
     <row r="509">
@@ -31496,7 +31496,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>9128.790000000001</v>
+        <v>9175.309999999999</v>
       </c>
     </row>
     <row r="510">
@@ -31557,7 +31557,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>3484.34</v>
+        <v>3502.09</v>
       </c>
     </row>
     <row r="511">
@@ -31618,13 +31618,13 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>1557.43</v>
+        <v>1565.37</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>2827-502-CM26</t>
+          <t>4451-384-CM26</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -31649,12 +31649,12 @@
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
@@ -31664,12 +31664,12 @@
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>GRUPO NUVIX SPA</t>
         </is>
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>76.202.065-3</t>
+          <t>78.209.441-6</t>
         </is>
       </c>
       <c r="K512" t="inlineStr"/>
@@ -31679,13 +31679,13 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>4039.23</v>
+        <v>1023.98</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>4451-384-CM26</t>
+          <t>1391-1294-CM26</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -31710,12 +31710,12 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>Dirección Regional de Gendarmeria - Talca</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
@@ -31725,12 +31725,12 @@
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>GRUPO NUVIX SPA</t>
+          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>78.209.441-6</t>
+          <t>78.906.980-8</t>
         </is>
       </c>
       <c r="K513" t="inlineStr"/>
@@ -31740,13 +31740,13 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>1029.2</v>
+        <v>1071.82</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>1391-1294-CM26</t>
+          <t>2827-502-CM26</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -31771,12 +31771,12 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
@@ -31786,12 +31786,12 @@
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
+          <t>MG Publicidad y Eventos SpA</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>78.906.980-8</t>
+          <t>76.202.065-3</t>
         </is>
       </c>
       <c r="K514" t="inlineStr"/>
@@ -31801,7 +31801,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>1077.27</v>
+        <v>4018.77</v>
       </c>
     </row>
     <row r="515">
@@ -31862,7 +31862,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>1713.6</v>
+        <v>1717.26</v>
       </c>
     </row>
     <row r="516">
@@ -31923,7 +31923,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>1799.44</v>
+        <v>1811.17</v>
       </c>
     </row>
     <row r="517">
@@ -31984,13 +31984,13 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>779.34</v>
+        <v>784.42</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>712830-81-CM26</t>
+          <t>1462-266-CM26</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -32010,17 +32010,17 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>61.606.906-3</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
         </is>
       </c>
       <c r="H518" t="inlineStr">
@@ -32030,12 +32030,12 @@
       </c>
       <c r="I518" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
         </is>
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>89.842.300-k</t>
         </is>
       </c>
       <c r="K518" t="inlineStr"/>
@@ -32045,13 +32045,13 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>937.33</v>
+        <v>1232.73</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>1681-511-CM26</t>
+          <t>2046-325-CM26</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -32076,12 +32076,12 @@
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.908-k</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
@@ -32091,12 +32091,12 @@
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
+          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>89.842.300-k</t>
+          <t>78.906.980-8</t>
         </is>
       </c>
       <c r="K519" t="inlineStr"/>
@@ -32106,13 +32106,13 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>19208.49</v>
+        <v>4910.46</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>2046-325-CM26</t>
+          <t>712830-81-CM26</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -32132,17 +32132,17 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>61.606.908-k</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
@@ -32152,12 +32152,12 @@
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>78.906.980-8</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K520" t="inlineStr"/>
@@ -32167,13 +32167,13 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>4899.23</v>
+        <v>939.48</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>1462-266-CM26</t>
+          <t>1681-511-CM26</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -32198,12 +32198,12 @@
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>61.606.906-3</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
@@ -32228,13 +32228,13 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>1229.91</v>
+        <v>19252.54</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>4401-547-CM26</t>
+          <t>1738-257-CM26</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -32259,12 +32259,12 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.130.200-8</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEGRE</t>
         </is>
       </c>
       <c r="H522" t="inlineStr">
@@ -32274,12 +32274,12 @@
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>AVA COMERCIAL SPA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>78.203.286-0</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K522" t="inlineStr"/>
@@ -32289,13 +32289,13 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>2716.89</v>
+        <v>5107.1</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>1738-257-CM26</t>
+          <t>1426095-163-CM26</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -32320,12 +32320,12 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>69.130.200-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEGRE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -32335,12 +32335,12 @@
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K523" t="inlineStr"/>
@@ -32350,13 +32350,13 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>5073.14</v>
+        <v>1440.63</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>4401-550-CM26</t>
+          <t>1069417-800-CM26</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -32376,17 +32376,17 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.270.200-k</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>Dirección  de Salud Municipal Chillán</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -32396,12 +32396,12 @@
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K524" t="inlineStr"/>
@@ -32411,13 +32411,13 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>2226.93</v>
+        <v>11539.94</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>4401-548-CM26</t>
+          <t>1978-717-CM26</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -32442,12 +32442,12 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -32457,12 +32457,12 @@
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>PROVEEDORA KENUA SPA</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J525" t="inlineStr">
         <is>
-          <t>78.212.867-1</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K525" t="inlineStr"/>
@@ -32472,13 +32472,13 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>1597.12</v>
+        <v>2567.99</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>4401-546-CM26</t>
+          <t>1978-718-CM26</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -32503,12 +32503,12 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">
@@ -32533,13 +32533,13 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>1088.61</v>
+        <v>2270.68</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>4401-549-CM26</t>
+          <t>1978-719-CM26</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -32564,12 +32564,12 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
@@ -32579,12 +32579,12 @@
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>MONARQUÍA SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>78.199.695-5</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K527" t="inlineStr"/>
@@ -32594,13 +32594,13 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>1978.56</v>
+        <v>6553.47</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>1978-718-CM26</t>
+          <t>4401-546-CM26</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -32625,12 +32625,12 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -32655,13 +32655,13 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>2255.59</v>
+        <v>1095.9</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>1978-717-CM26</t>
+          <t>4401-547-CM26</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -32686,12 +32686,12 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -32701,12 +32701,12 @@
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>AVA COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J529" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>78.203.286-0</t>
         </is>
       </c>
       <c r="K529" t="inlineStr"/>
@@ -32716,13 +32716,13 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>2550.91</v>
+        <v>2735.08</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>1978-719-CM26</t>
+          <t>4401-548-CM26</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -32747,12 +32747,12 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
@@ -32762,12 +32762,12 @@
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>PROVEEDORA KENUA SPA</t>
         </is>
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.212.867-1</t>
         </is>
       </c>
       <c r="K530" t="inlineStr"/>
@@ -32777,13 +32777,13 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>6509.89</v>
+        <v>1607.81</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>1069417-800-CM26</t>
+          <t>4401-549-CM26</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -32803,17 +32803,17 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>69.270.200-k</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
@@ -32823,12 +32823,12 @@
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>MONARQUÍA SPA</t>
         </is>
       </c>
       <c r="J531" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.199.695-5</t>
         </is>
       </c>
       <c r="K531" t="inlineStr"/>
@@ -32838,13 +32838,13 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>11463.21</v>
+        <v>1991.8</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>1426095-163-CM26</t>
+          <t>4401-550-CM26</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -32869,12 +32869,12 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
@@ -32884,12 +32884,12 @@
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J532" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K532" t="inlineStr"/>
@@ -32899,13 +32899,13 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>1431.05</v>
+        <v>2241.84</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>3287-352-CM26</t>
+          <t>1075337-8988-CM26</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -32925,17 +32925,17 @@
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
@@ -32945,12 +32945,12 @@
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.906.980-8</t>
         </is>
       </c>
       <c r="K533" t="inlineStr"/>
@@ -32960,13 +32960,13 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>1839</v>
+        <v>9914.620000000001</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>1075337-8988-CM26</t>
+          <t>1681-518-CM26</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -32991,12 +32991,12 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
@@ -33006,12 +33006,12 @@
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
+          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
         </is>
       </c>
       <c r="J534" t="inlineStr">
         <is>
-          <t>78.906.980-8</t>
+          <t>89.842.300-k</t>
         </is>
       </c>
       <c r="K534" t="inlineStr"/>
@@ -33021,13 +33021,13 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>9845.719999999999</v>
+        <v>1798.22</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>1681-518-CM26</t>
+          <t>3287-352-CM26</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -33047,17 +33047,17 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
@@ -33067,12 +33067,12 @@
       </c>
       <c r="I535" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J535" t="inlineStr">
         <is>
-          <t>89.842.300-k</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K535" t="inlineStr"/>
@@ -33082,13 +33082,13 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>1785.73</v>
+        <v>1851.87</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>1465-315-CM26</t>
+          <t>4716-12-CM26</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -33113,12 +33113,12 @@
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>61.606.907-1</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
@@ -33128,12 +33128,12 @@
       </c>
       <c r="I536" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t>89.842.300-k</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K536" t="inlineStr"/>
@@ -33143,7 +33143,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>2557.78</v>
+        <v>1662.28</v>
       </c>
     </row>
     <row r="537">
@@ -33204,13 +33204,13 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>1179.96</v>
+        <v>1176.23</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>4716-12-CM26</t>
+          <t>1465-315-CM26</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -33235,12 +33235,12 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.606.907-1</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
@@ -33250,12 +33250,12 @@
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
         </is>
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>89.842.300-k</t>
         </is>
       </c>
       <c r="K538" t="inlineStr"/>
@@ -33265,7 +33265,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>1667.54</v>
+        <v>2549.7</v>
       </c>
     </row>
     <row r="539">
@@ -33326,7 +33326,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>936.39</v>
+        <v>934.35</v>
       </c>
     </row>
     <row r="540">
@@ -33387,7 +33387,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>12462.81</v>
+        <v>12437.82</v>
       </c>
     </row>
     <row r="541">
@@ -33448,7 +33448,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>2115.69</v>
+        <v>2111.45</v>
       </c>
     </row>
     <row r="542">
@@ -33509,7 +33509,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>912.72</v>
+        <v>910.89</v>
       </c>
     </row>
     <row r="543">
@@ -33570,7 +33570,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>2944.72</v>
+        <v>2938.82</v>
       </c>
     </row>
     <row r="544">
@@ -33631,7 +33631,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>3793.37</v>
+        <v>3785.77</v>
       </c>
     </row>
     <row r="545">
@@ -33692,13 +33692,13 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>1464.89</v>
+        <v>1456.41</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>1069417-839-CM26</t>
+          <t>362-400-CM26</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -33723,12 +33723,12 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>69.270.200-k</t>
+          <t>61.606.915-2</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
@@ -33738,12 +33738,12 @@
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K546" t="inlineStr"/>
@@ -33753,13 +33753,13 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>3115.16</v>
+        <v>1762.29</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>362-400-CM26</t>
+          <t>1069417-839-CM26</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -33784,12 +33784,12 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>61.606.915-2</t>
+          <t>69.270.200-k</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Dirección  de Salud Municipal Chillán</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -33799,12 +33799,12 @@
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J547" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K547" t="inlineStr"/>
@@ -33814,13 +33814,13 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>1772.55</v>
+        <v>3097.13</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>4089-423-CM26</t>
+          <t>4089-427-CM26</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -33875,13 +33875,13 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>782.89</v>
+        <v>2015.51</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>4089-427-CM26</t>
+          <t>4089-423-CM26</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -33936,7 +33936,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>2027.25</v>
+        <v>778.36</v>
       </c>
     </row>
     <row r="550">
@@ -33997,7 +33997,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>1883.79</v>
+        <v>1872.89</v>
       </c>
     </row>
     <row r="551">
@@ -34058,7 +34058,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>8603.459999999999</v>
+        <v>8464.620000000001</v>
       </c>
     </row>
     <row r="552">
@@ -34119,7 +34119,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>1866.23</v>
+        <v>1836.11</v>
       </c>
     </row>
     <row r="553">
@@ -34180,7 +34180,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>3134.95</v>
+        <v>3084.36</v>
       </c>
     </row>
     <row r="554">
@@ -34241,7 +34241,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>1134.18</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="555">
@@ -34302,7 +34302,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>13807.66</v>
+        <v>13586.28</v>
       </c>
     </row>
     <row r="556">
@@ -34363,7 +34363,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>1172.27</v>
+        <v>1158.63</v>
       </c>
     </row>
     <row r="557">
@@ -34424,7 +34424,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>2943.5</v>
+        <v>2927.18</v>
       </c>
     </row>
     <row r="558">
@@ -34485,7 +34485,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>1391.5</v>
+        <v>1383.79</v>
       </c>
     </row>
     <row r="559">
@@ -34546,7 +34546,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>26086.25</v>
+        <v>25941.63</v>
       </c>
     </row>
     <row r="560">
@@ -34607,7 +34607,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>1767.21</v>
+        <v>1758.52</v>
       </c>
     </row>
     <row r="561">
@@ -34668,7 +34668,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>2501.89</v>
+        <v>2489.59</v>
       </c>
     </row>
     <row r="562">
@@ -34729,7 +34729,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>912.3200000000001</v>
+        <v>907.83</v>
       </c>
     </row>
     <row r="563">
@@ -34790,7 +34790,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>3090.58</v>
+        <v>3111.27</v>
       </c>
     </row>
     <row r="564">
@@ -34851,7 +34851,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>32359.25</v>
+        <v>32575.85</v>
       </c>
     </row>
     <row r="565">
@@ -34912,7 +34912,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>13303.5</v>
+        <v>13392.55</v>
       </c>
     </row>
     <row r="566">
@@ -34973,7 +34973,312 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>3297.85</v>
+        <v>3319.92</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>4172-404-CM26</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>69.130.500-7</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr"/>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M567" s="2" t="n">
+        <v>2216.37</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>4605-92-CM26</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>61.819.000-5</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION VII REGION</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr"/>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M568" s="2" t="n">
+        <v>5893.53</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>4452-646-CM26</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>61.606.903-9</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>Barron Vieyra International Ltda.</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>78.723.570-0</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr"/>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M569" s="2" t="n">
+        <v>18662.64</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>1978-878-CM26</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>61.606.900-4</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr"/>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M570" s="2" t="n">
+        <v>10153.09</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>3806-131-CM26</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>69.120.200-3</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE EMPEDRADO</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>78.906.980-8</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr"/>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M571" s="2" t="n">
+        <v>1310.32</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/maule.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/maule.xlsx
@@ -1923,7 +1923,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2049,7 +2053,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2427,7 +2435,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2553,7 +2565,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2614,7 +2630,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2992,7 +3012,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3118,7 +3142,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3894,7 +3922,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4150,7 +4182,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4276,7 +4312,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4662,7 +4702,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5608,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5881,7 +5929,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6519,7 +6571,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6710,7 +6766,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6836,7 +6896,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7413,7 +7477,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7604,7 +7672,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8181,7 +8253,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8823,7 +8899,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11184,7 +11264,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11822,7 +11906,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11948,7 +12036,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13293,7 +13385,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13419,7 +13515,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13663,7 +13763,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13919,7 +14023,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14045,7 +14153,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14171,7 +14283,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14358,7 +14474,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15126,7 +15246,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15187,7 +15311,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15248,7 +15376,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15374,7 +15506,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15500,7 +15636,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15691,7 +15831,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16142,7 +16286,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16398,7 +16546,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16524,7 +16676,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16650,7 +16806,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16711,7 +16871,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17800,7 +17964,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17861,7 +18029,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18304,7 +18476,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18690,7 +18866,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18938,7 +19118,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18999,7 +19183,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19320,7 +19508,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21051,7 +21243,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21177,7 +21373,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21238,7 +21438,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21994,7 +22198,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22242,7 +22450,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22303,7 +22515,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22494,7 +22710,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +23352,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23514,7 +23738,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24022,7 +24250,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24083,7 +24315,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25176,7 +25412,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25237,7 +25477,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25623,7 +25867,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25944,7 +26192,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26005,7 +26257,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30576,7 +30832,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33091,7 +33351,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33993,7 +34257,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34830,7 +35098,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38251,7 +38523,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38958,7 +39234,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39019,7 +39299,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39080,7 +39364,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39462,7 +39750,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39588,7 +39880,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40104,7 +40400,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42103,7 +42403,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42554,7 +42858,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43066,7 +43374,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44167,7 +44479,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44358,7 +44674,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45886,7 +46206,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L710" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45947,7 +46271,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46138,7 +46466,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46264,7 +46596,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L716" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47097,7 +47433,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L729" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47288,7 +47628,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K732" t="inlineStr"/>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L732" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47349,7 +47693,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47532,7 +47880,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K736" t="inlineStr"/>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L736" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47593,7 +47945,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K737" t="inlineStr"/>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L737" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47784,7 +48140,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K740" t="inlineStr"/>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L740" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48560,7 +48920,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K752" t="inlineStr"/>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L752" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48621,7 +48985,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K753" t="inlineStr"/>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L753" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48682,7 +49050,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L754" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49320,7 +49692,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K764" t="inlineStr"/>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L764" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49771,7 +50147,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K771" t="inlineStr"/>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L771" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49832,7 +50212,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K772" t="inlineStr"/>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L772" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50149,7 +50533,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K777" t="inlineStr"/>
+      <c r="K777" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L777" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50210,7 +50598,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K778" t="inlineStr"/>
+      <c r="K778" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L778" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52022,7 +52414,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K806" t="inlineStr"/>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L806" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53046,7 +53442,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K822" t="inlineStr"/>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L822" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53233,7 +53633,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K825" t="inlineStr"/>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L825" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53420,7 +53824,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K828" t="inlineStr"/>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L828" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54704,7 +55112,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K848" t="inlineStr"/>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L848" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55090,7 +55502,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K854" t="inlineStr"/>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L854" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55281,7 +55697,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K857" t="inlineStr"/>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L857" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55797,7 +56217,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K865" t="inlineStr"/>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L865" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57219,7 +57643,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K887" t="inlineStr"/>
+      <c r="K887" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L887" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57280,7 +57708,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K888" t="inlineStr"/>
+      <c r="K888" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L888" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57666,7 +58098,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K894" t="inlineStr"/>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L894" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59478,7 +59914,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K922" t="inlineStr"/>
+      <c r="K922" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L922" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59539,7 +59979,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K923" t="inlineStr"/>
+      <c r="K923" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L923" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60571,7 +61015,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K939" t="inlineStr"/>
+      <c r="K939" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L939" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60957,7 +61405,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K945" t="inlineStr"/>
+      <c r="K945" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L945" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63021,7 +63473,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K977" t="inlineStr"/>
+      <c r="K977" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L977" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63598,7 +64054,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K986" t="inlineStr"/>
+      <c r="K986" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L986" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63854,7 +64314,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K990" t="inlineStr"/>
+      <c r="K990" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L990" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64041,7 +64505,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K993" t="inlineStr"/>
+      <c r="K993" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L993" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64102,7 +64570,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K994" t="inlineStr"/>
+      <c r="K994" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L994" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64813,7 +65285,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1005" t="inlineStr"/>
+      <c r="K1005" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1005" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65264,7 +65740,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1012" t="inlineStr"/>
+      <c r="K1012" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1012" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65325,7 +65805,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1013" t="inlineStr"/>
+      <c r="K1013" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1013" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65386,7 +65870,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1014" t="inlineStr"/>
+      <c r="K1014" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1014" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65577,7 +66065,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1017" t="inlineStr"/>
+      <c r="K1017" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1017" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66284,7 +66776,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1028" t="inlineStr"/>
+      <c r="K1028" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1028" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66926,7 +67422,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1038" t="inlineStr"/>
+      <c r="K1038" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1038" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67828,7 +68328,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1052" t="inlineStr"/>
+      <c r="K1052" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1052" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67954,7 +68458,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1054" t="inlineStr"/>
+      <c r="K1054" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1054" t="inlineStr">
         <is>
           <t>USD</t>
@@ -69112,7 +69620,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1072" t="inlineStr"/>
+      <c r="K1072" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1072" t="inlineStr">
         <is>
           <t>USD</t>
